--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -624,7 +624,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">259
@@ -633,50 +638,45 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -715,7 +715,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
@@ -727,12 +727,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>132</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>125</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -765,7 +765,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4645
+</t>
+        </is>
+      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>2651</t>
@@ -773,7 +778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -813,7 +818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -826,36 +831,38 @@
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">77
+990
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1839
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
@@ -885,13 +892,13 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -909,13 +916,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
+          <t xml:space="preserve">389
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -933,14 +940,10 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>01400</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">12
@@ -949,13 +952,13 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -966,38 +969,37 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8261
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1015,7 +1017,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1025,19 +1027,19 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">9310
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1055,7 +1057,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3552
 </t>
         </is>
       </c>
@@ -1079,54 +1081,57 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1671
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1138,7 +1143,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1150,13 +1155,13 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -1168,25 +1173,25 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1204,7 +1209,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3279
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -1222,62 +1227,60 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2131
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13189
+          <t xml:space="preserve">127219
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
@@ -1295,13 +1298,13 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1319,7 +1322,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
@@ -1331,7 +1334,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -1350,7 +1353,8 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1366,43 +1370,51 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t xml:space="preserve">1342
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
-</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="n"/>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -1415,13 +1427,13 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">8929
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">056
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
@@ -1445,7 +1457,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
@@ -1457,7 +1469,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1472,31 +1484,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1506,17 +1516,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
@@ -1529,63 +1539,67 @@
 </t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16379
+</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">430
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">541
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1914
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1901
 </t>
         </is>
       </c>
@@ -1597,7 +1611,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1615,113 +1629,127 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n"/>
+          <t xml:space="preserve">77871
+</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2531
+228548177
+</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11975
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>017</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">895
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1736,67 +1764,63 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>041</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1789
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">277275
+163
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1808,19 +1832,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8589
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -1838,25 +1862,24 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">8850
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1874,19 +1897,20 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1897,63 +1921,58 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">001
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -1962,16 +1981,16 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">292
+</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">192
 </t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">668
@@ -1980,7 +1999,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
@@ -1998,17 +2017,22 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
-        </is>
-      </c>
-      <c r="Z13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>8</t>
@@ -2024,7 +2048,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2036,117 +2060,123 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">232
+</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4445</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3561
+</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9908
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9979
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2065
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">23
 </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1144</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">845
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -2165,13 +2195,13 @@
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2183,13 +2213,14 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2200,16 +2231,11 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3252
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
           <t>44</t>
@@ -2217,20 +2243,25 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184883
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9226
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr"/>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2248,13 +2279,13 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -2265,12 +2296,12 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>83</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2298,16 +2329,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2319,25 +2350,25 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">4236
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4819
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -2349,81 +2380,82 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>121</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">9416
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>553</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,7 +2473,8 @@
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t xml:space="preserve">2579
+</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2452,8 +2485,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2464,13 +2496,13 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">4891
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -2480,41 +2512,30 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>222</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">034
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4381
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2523,30 +2544,29 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
-</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -2558,7 +2578,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11909
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -2570,7 +2590,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -2595,30 +2615,31 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">98
 </t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2630,7 +2651,8 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>03</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -2642,76 +2664,72 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9986
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>124</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7420
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr"/>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>6340880</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2726,58 +2744,70 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 85 2
+</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1921
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+      <c r="P19" s="2" t="inlineStr"/>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2788,13 +2818,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">740
 </t>
         </is>
       </c>
@@ -2806,7 +2835,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>195</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2817,13 +2846,13 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2854,22 +2883,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">93
@@ -2878,7 +2902,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -2890,24 +2914,24 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2919,58 +2943,53 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>131</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1912
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr"/>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -2995,12 +3014,13 @@
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>372</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -3012,7 +3032,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3024,102 +3044,102 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">32
+</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
-</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -3138,7 +3158,8 @@
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3149,64 +3170,65 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">165
 </t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11888
-</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">246
@@ -3221,49 +3243,49 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2891
+</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1892
+</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">889
-</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3293,25 +3315,25 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -3335,30 +3357,36 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9700
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">066
+</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -3371,14 +3399,13 @@
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
-</t>
+          <t>492</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3395,7 +3422,8 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">261
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3406,7 +3434,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>763</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3421,30 +3449,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1256
-</t>
-        </is>
-      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>531</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3455,15 +3482,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7017
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3474,17 +3500,16 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">928
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">231
@@ -3493,55 +3518,54 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">3281
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">1731
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>9300407</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3558,55 +3582,41 @@
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122 1
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">372
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3617,69 +3627,48 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111561
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1108
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr"/>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr"/>
-      <c r="Y25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4158
+41419
+</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="n"/>
+      <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3692,68 +3681,64 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">115178685
+1149791
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>016</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">08
 </t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>153</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -3765,60 +3750,62 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">850
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">10
 </t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr"/>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3834,128 +3821,133 @@
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">7155
+</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">379
+</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">153
 </t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>043</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1128
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3971,16 +3963,21 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -3990,15 +3987,10 @@
 </t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -4009,93 +4001,84 @@
 </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21610
+</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">9360
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4114,129 +4097,131 @@
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>4241</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">990
 </t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>4343</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1310
-</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="Y29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">910
-</t>
-        </is>
-      </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4252,40 +4237,39 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11168
-</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4294,92 +4278,99 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">2150
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1998
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42138
+          <t xml:space="preserve">667
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>42501</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4396,46 +4387,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+89191911
+</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">769
@@ -4444,63 +4436,70 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t>99921</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">2272
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1081
-</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">959
+</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4132
+</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>415</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">852
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
@@ -4512,13 +4511,12 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4535,53 +4533,42 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0884
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144 1
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">904
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">943
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">150
@@ -4590,79 +4577,83 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">81429988448
+8
+771141
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">4781
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">19 1 6
+</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70 6
+</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 84
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">951
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 13
+          <t xml:space="preserve">81911955
+111
 </t>
         </is>
       </c>
@@ -4680,23 +4671,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
+          <t xml:space="preserve">3646
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">441
+</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4707,101 +4701,107 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">7116
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2007
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">18 1
 </t>
         </is>
       </c>
@@ -4817,71 +4817,73 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4402
+</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">839
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -4890,51 +4892,56 @@
           <t>212</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4950,10 +4957,16 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
+</t>
+        </is>
+      </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4964,30 +4977,29 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -4999,20 +5011,25 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">452
+</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -5024,60 +5041,55 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">9868
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5096,18 +5108,18 @@
       <c r="C36" s="2" t="n"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
@@ -5119,7 +5131,8 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -5130,50 +5143,53 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -5184,42 +5200,43 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5238,7 +5255,7 @@
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5260,102 +5277,115 @@
 </t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1079
+</t>
+        </is>
+      </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">759
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2191
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9878
-</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">590
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">899
-</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>38191</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr"/>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">4225
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5371,119 +5401,131 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>44841</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="n"/>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6813
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">676
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">525
+</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">4960
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10180
-</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8792
+</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
+          <t xml:space="preserve">3809
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t xml:space="preserve">816
+</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>74</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5499,8 +5541,17 @@
           <t>26</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -5513,34 +5564,40 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="2" t="n"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">820
+</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
+          <t xml:space="preserve">21372
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5551,36 +5608,68 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">924
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1084
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="n"/>
-      <c r="T39" s="2" t="n"/>
-      <c r="U39" s="2" t="n"/>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">661
+</t>
+        </is>
+      </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="n"/>
-      <c r="X39" s="2" t="n"/>
-      <c r="Y39" s="2" t="n"/>
-      <c r="Z39" s="2" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>26</t>
@@ -5595,125 +5684,132 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t xml:space="preserve">227
+6443
+</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">722
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">789
+</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5729,20 +5825,16 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6377
-</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -5754,11 +5846,15 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">38
@@ -5773,22 +5869,17 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">700
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">120
@@ -5803,7 +5894,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -5815,53 +5906,54 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">1726
+</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">488
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5879,13 +5971,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4088
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -5898,51 +5990,47 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">472
+</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">56
-</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1013
-</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1123
-</t>
-        </is>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5957,55 +6045,50 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">089
-</t>
-        </is>
-      </c>
+      <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
@@ -6023,121 +6106,129 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">60944
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>110411</t>
+          <t xml:space="preserve">7064
+</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t xml:space="preserve">80
+</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">7119
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr"/>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">498
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">532
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6155,7 +6246,8 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">622
+2722208602828
 </t>
         </is>
       </c>
@@ -6167,25 +6259,15 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1017
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111416 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2124
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -6201,38 +6283,33 @@
 </t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>30</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -6242,50 +6319,27 @@
 </t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24222
+7
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">422
 </t>
         </is>
       </c>
@@ -6308,14 +6362,24 @@
 </t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">672727
+</t>
+        </is>
+      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr"/>
+          <t>534</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+24222
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">775
@@ -6324,39 +6388,39 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">550020
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">6022
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6219
+          <t xml:space="preserve">61972
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101101101
+          <t xml:space="preserve">6242
 </t>
         </is>
       </c>
@@ -6369,40 +6433,56 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10110
+          <t xml:space="preserve">8272
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501151000115
-</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2181
+</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119898
-</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr"/>
-      <c r="X45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">12089
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">832
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
+          <t xml:space="preserve">378
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">87
+</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6419,18 +6499,20 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t xml:space="preserve">321
+</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t xml:space="preserve">107
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6453,7 +6535,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">3821
 </t>
         </is>
       </c>
@@ -6463,36 +6545,35 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">559
+</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4980
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">253
@@ -6501,49 +6582,39 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">831
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">881
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">929180
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
+      <c r="X46" s="2" t="n"/>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6562,72 +6633,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>231</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1044
-</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">505
-</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1684
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,56 +632,62 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">71138
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2108
+</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -693,18 +699,19 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">12668
+</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>211</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -715,44 +722,20 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n"/>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">930
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="n"/>
+      <c r="X4" s="2" t="n"/>
+      <c r="Y4" s="2" t="n"/>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -767,24 +750,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
+          <t xml:space="preserve">15643
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2651</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -795,18 +778,18 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -818,7 +801,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1140
 </t>
         </is>
       </c>
@@ -828,41 +811,39 @@
 </t>
         </is>
       </c>
-      <c r="N5" s="2" t="n"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-990
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1839
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -874,32 +855,30 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">2930
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -916,20 +895,19 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">389
+          <t xml:space="preserve">3380
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -940,25 +918,30 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01400</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111416
+</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -969,43 +952,42 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">09942
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1161
+</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">6718
 </t>
         </is>
       </c>
@@ -1017,29 +999,29 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>120</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9310
+          <t xml:space="preserve">1930
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">11039
 </t>
         </is>
       </c>
@@ -1057,7 +1039,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3552
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1069,129 +1051,112 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2801
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+          <t xml:space="preserve">2985
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">94
 </t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="n"/>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1209,132 +1174,132 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3779
+</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2121
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149712
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">72
 </t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127219
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">19178
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">1850
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -1350,71 +1315,70 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1825281
+</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>451</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>741</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1427,49 +1391,51 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8929
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t xml:space="preserve">9988
+</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">8712
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
+          <t xml:space="preserve">194290
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t xml:space="preserve">161
+</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1484,45 +1450,40 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3650
+</t>
+        </is>
+      </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1535,71 +1496,53 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16379
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">430
-</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">986
+</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">541
-</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
+      <c r="W10" s="2" t="n"/>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1611,7 +1554,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">382
 </t>
         </is>
       </c>
@@ -1629,127 +1572,127 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77871
+          <t xml:space="preserve">3296
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2531
-228548177
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t xml:space="preserve">1107
+</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1426
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">12895
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">720
+</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t xml:space="preserve">1186
+</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t xml:space="preserve">1181
+</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1764,64 +1707,81 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">5212
+</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
+          <t xml:space="preserve">2317
+</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>041</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277275
-163
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2999
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1832,19 +1792,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">2172
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1469
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
@@ -1856,30 +1816,31 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -1897,44 +1858,41 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">94556
+</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">21138
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1945,34 +1903,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t xml:space="preserve">17176
+</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">238
@@ -1981,25 +1944,24 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -2011,25 +1973,25 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2045,79 +2007,81 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203199
+</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">129
+</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3561
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9908
+          <t xml:space="preserve">18202
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9979
+          <t xml:space="preserve">9290
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2139,44 +2103,34 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2065
-</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="n"/>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
@@ -2192,7 +2146,12 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4845
+</t>
+        </is>
+      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">267
@@ -2201,110 +2160,94 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11007
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3252
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184883
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9226
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>412</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+      <c r="X15" s="2" t="n"/>
       <c r="Y15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">848
@@ -2313,7 +2256,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2331,44 +2274,43 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">23269
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1272
 </t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
+          <t xml:space="preserve">2957
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4236
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1954819
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2380,82 +2322,89 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1669
+</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">194910
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t xml:space="preserve">929
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">3130
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t xml:space="preserve">9290
+</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2470,72 +2419,76 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">2592
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">653
-</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">11191
+</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">18241
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4891
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1139
+</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4381
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">237
@@ -2544,53 +2497,53 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>41</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1183
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
+          <t xml:space="preserve">5626
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t xml:space="preserve">1112
+</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8980
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2974
 </t>
         </is>
       </c>
@@ -2606,22 +2559,27 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3357
+</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1143
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -2633,103 +2591,89 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1940
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t xml:space="preserve">1229
+</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">27190
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2102
+</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">5167
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>6340880</t>
+          <t>62</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2746,68 +2690,74 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 85 2
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">111626
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1138
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1968
+</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2823,36 +2773,32 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t xml:space="preserve">1199
+</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1175
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8948
 </t>
         </is>
       </c>
@@ -2874,76 +2820,70 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">112494
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="n"/>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">126
+</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2954,48 +2894,44 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">175
+</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1167
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr"/>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t>434</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="n"/>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -3011,46 +2947,56 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3793
+</t>
+        </is>
+      </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n"/>
+          <t xml:space="preserve">11796
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1188
+</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">2888
+</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -3062,24 +3008,20 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3091,7 +3033,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3101,48 +3043,33 @@
 </t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+      <c r="T21" s="2" t="n"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">11694
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="n"/>
+      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3155,140 +3082,126 @@
           <t>15</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5089
+</t>
+        </is>
+      </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>458</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">21132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="n"/>
+          <t xml:space="preserve">1295
+</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">517
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="n"/>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3303,138 +3216,137 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">20894
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">11285
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">11614
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">539
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">696
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">294890
+</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">066
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">11136
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr"/>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">23280
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>492</t>
+          <t xml:space="preserve">12198
+</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">1863
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3451,124 +3363,110 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t xml:space="preserve">4379 18
+</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10256
+</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6215659
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>44</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2399
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="n"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3281
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1731
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n"/>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>9300407</t>
+          <t xml:space="preserve">188812
+</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="n"/>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3581,94 +3479,132 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2336
+</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122 1
-</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="n"/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28726
+</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1136
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">108
 </t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">372
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="n"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="n"/>
+          <t xml:space="preserve">1020
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="n"/>
+          <t xml:space="preserve">5189
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="U25" s="2" t="n"/>
-      <c r="V25" s="2" t="n"/>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4158
-41419
-</t>
-        </is>
-      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="Y25" s="2" t="n"/>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3681,128 +3617,136 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2583
+</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115178685
-1149791
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>016</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1828
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
+          <t xml:space="preserve">1010
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9318
+</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">0153
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">016
 </t>
         </is>
       </c>
@@ -3818,136 +3762,125 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5358
+</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">12245
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7155
+          <t xml:space="preserve">7133
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">11189
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">379
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20916
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">11835
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="n"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="n"/>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3965,120 +3898,126 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="n"/>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21610
-</t>
-        </is>
-      </c>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1328
+</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>445</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9360
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4094,134 +4033,129 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3091
+</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t xml:space="preserve">236
+</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="n"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8561
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">119910
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4237,140 +4171,130 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15699
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t xml:space="preserve">719
+</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">15449
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">16294
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">45
+</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1769
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2150
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>4449244</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">2121
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">667
+          <t xml:space="preserve">94138
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">9220
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4387,136 +4311,130 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">3140
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-89191911
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">769
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">084
+</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1150
+</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t xml:space="preserve">859
+</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">024
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2272
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4132
+          <t xml:space="preserve">81154
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">852
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
+          <t xml:space="preserve">1063
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">1 85
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>42221</t>
+          <t xml:space="preserve">950
+</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4533,130 +4451,105 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t xml:space="preserve">3642
+</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2579
+</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n"/>
+          <t xml:space="preserve">128213
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-</t>
+          <t>391</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">7196
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81429988448
-8
-771141
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4781
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19 1 6
-</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1148
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="n"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70 6
-</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="n"/>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">951
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81911955
-111
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="n"/>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4671,137 +4564,126 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3646
+          <t xml:space="preserve">4112
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11000
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">143
 </t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7116
-</t>
-        </is>
-      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">110972
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">201912
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="n"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">2916
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">19800
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 1
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -4819,129 +4701,121 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4402
-</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">151
+</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">174
+</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t xml:space="preserve">946
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11452
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">169
+</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">778
-</t>
-        </is>
-      </c>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="n"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>432</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -4959,137 +4833,135 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">1121
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1112
+</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">1212818
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9868
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>484</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>65</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">2840
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5105,138 +4977,133 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6132
+</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1138
+</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
-</t>
+          <t>4495</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t xml:space="preserve">11150
+</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">11616
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>412</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5252,141 +5119,142 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>197824</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">10922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">523
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">569
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1501
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">16815
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">1676
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">94920
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">1899
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">889
+</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2191
-</t>
+          <t>3821914</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2332
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t xml:space="preserve">1816
+</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4225
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5403,129 +5271,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>44841</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4956
+</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">1741
+</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">1913
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">525
-</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2190
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4960
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>302</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8792
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">11720
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">762
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">1664
+</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">816
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">181014
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">01846
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -5543,127 +5404,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">6243
+</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21372
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t xml:space="preserve">2193
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">121202
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">924
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
+          <t xml:space="preserve">2012
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1505
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="n"/>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1988
+</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1679
+</t>
+        </is>
+      </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">32
@@ -5684,25 +5539,25 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-6443
+          <t xml:space="preserve">6377
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t xml:space="preserve">1260
+</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5712,59 +5567,64 @@
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">11100
+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1219
+</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">2354
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -5775,41 +5635,42 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">0488
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">1169
+</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
+          <t xml:space="preserve">1628
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -5825,135 +5686,116 @@
           <t>28</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7943
+</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">397
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1181
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1013
+</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11208
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">881
+</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">179
 </t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1726
-</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">420
-</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t xml:space="preserve">2 1 4
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5977,39 +5819,49 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24709
+</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">11224
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n"/>
+          <t xml:space="preserve">11605
+</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">472
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6019,24 +5871,14 @@
 </t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
+      <c r="M42" s="2" t="n"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">932
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -6045,15 +5887,25 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
+          <t xml:space="preserve">9490
 </t>
         </is>
       </c>
@@ -6065,30 +5917,31 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">11686
+</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6106,79 +5959,71 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60944
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7064
-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1810
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7119
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">178
@@ -6193,19 +6038,19 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
@@ -6216,19 +6061,19 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
+          <t xml:space="preserve">7298
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6244,106 +6089,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">622
-2722208602828
-</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2124
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24222
-7
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr"/>
-      <c r="X44" s="2" t="inlineStr"/>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">422
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6364,19 +6133,18 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">672727
-</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t xml:space="preserve">036
+</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-24222
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6388,100 +6156,113 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11819
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1800
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6022
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3564
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">559
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">61972
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6242
-</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr"/>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">11263
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12089
+          <t xml:space="preserve">11089
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">10609
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">378
+          <t xml:space="preserve">23028 1
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6499,31 +6280,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2239
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>405</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">15034
 </t>
         </is>
       </c>
@@ -6535,89 +6315,81 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3821
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t xml:space="preserve">11113
+</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">139
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">2353
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1178
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="n"/>
       <c r="U46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18654
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2184
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929180
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
-      <c r="X46" s="2" t="n"/>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
+      <c r="Y46" s="2" t="n"/>
       <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
@@ -6629,42 +6401,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">551
-</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,13 +632,13 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
@@ -648,16 +648,21 @@
 </t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -669,7 +674,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -681,13 +686,13 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -699,19 +704,20 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">8202
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12668
+          <t xml:space="preserve">8197
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1893
+</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -726,16 +732,42 @@
 </t>
         </is>
       </c>
-      <c r="U4" s="2" t="n"/>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="n"/>
-      <c r="X4" s="2" t="n"/>
-      <c r="Y4" s="2" t="n"/>
-      <c r="Z4" s="2" t="n"/>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1120
+</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">930
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -750,19 +782,20 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15643
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1140
+</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -773,7 +806,8 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -784,24 +818,25 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -819,19 +854,25 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
+          <t xml:space="preserve">958
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>213</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -855,30 +896,32 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -901,29 +944,31 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">19
+</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111416
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
@@ -935,30 +980,31 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09942
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1215621
 </t>
         </is>
       </c>
@@ -968,7 +1014,12 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -977,17 +1028,19 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6718
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
@@ -999,29 +1052,31 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1930
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11039
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1039,7 +1094,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
+          <t xml:space="preserve">2552
 </t>
         </is>
       </c>
@@ -1051,7 +1106,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -1063,23 +1118,25 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1091,12 +1148,14 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1107,11 +1166,16 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2985
-</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">200
@@ -1120,10 +1184,16 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="n"/>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">770
@@ -1138,19 +1208,25 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="n"/>
+          <t xml:space="preserve">170
+</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1174,7 +1250,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
+          <t xml:space="preserve">3778
 </t>
         </is>
       </c>
@@ -1192,47 +1268,55 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n"/>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t xml:space="preserve">142
+</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1152
+</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149712
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
@@ -1244,26 +1328,31 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -1275,13 +1364,13 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19178
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -1293,13 +1382,13 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1850
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -1317,17 +1406,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825281
+          <t xml:space="preserve">18252
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n"/>
+          <t xml:space="preserve">1265
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">715
+</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -1336,13 +1430,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">050
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">615
 </t>
         </is>
       </c>
@@ -1354,38 +1448,49 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">12819
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">891
+</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4238
+</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1397,20 +1502,25 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">9856
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9988
-</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr"/>
+          <t xml:space="preserve">09101
+</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">955
 </t>
         </is>
       </c>
@@ -1422,19 +1532,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">9498
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194290
+          <t xml:space="preserve">942908
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -1452,7 +1562,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">36501
 </t>
         </is>
       </c>
@@ -1464,17 +1574,28 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">13
@@ -1483,26 +1604,31 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="n"/>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -1512,10 +1638,15 @@
 </t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83 8
+</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1537,9 +1668,23 @@
 </t>
         </is>
       </c>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n"/>
-      <c r="W10" s="2" t="n"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1174
+</t>
+        </is>
+      </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -1548,13 +1693,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">382
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1582,8 +1727,18 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1139
+</t>
+        </is>
+      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">101
@@ -1592,67 +1747,73 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">097
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n"/>
+          <t xml:space="preserve">1128
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">527
+</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1426
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18114</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12895
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1664,13 +1825,13 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -1682,17 +1843,22 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr"/>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>6</t>
@@ -1707,104 +1873,109 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5212
+          <t xml:space="preserve">5811
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2317
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2539
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2198
+</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">018
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0800
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">090
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1139
 </t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1222
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1249
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2999
-</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2172
-</t>
-        </is>
-      </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1469
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">141046
 </t>
         </is>
       </c>
@@ -1816,13 +1987,13 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -1834,13 +2005,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -1858,7 +2029,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94556
+          <t xml:space="preserve">5556
 </t>
         </is>
       </c>
@@ -1870,29 +2041,32 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t xml:space="preserve">2216
+</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21138
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">86
+</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1909,30 +2083,31 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17176
+          <t xml:space="preserve">8196
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1944,7 +2119,8 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1955,16 +2131,11 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -1973,13 +2144,13 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">078
+          <t xml:space="preserve">1978
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -1991,7 +2162,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2009,7 +2180,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203199
+          <t xml:space="preserve">0318
 </t>
         </is>
       </c>
@@ -2021,67 +2192,73 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t xml:space="preserve">2045
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t xml:space="preserve">1125
+</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">125
+</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18202
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -2103,25 +2280,36 @@
 </t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
+</t>
+        </is>
+      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="n"/>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">840
@@ -2130,7 +2318,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2160,47 +2348,64 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11007
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
+          <t xml:space="preserve">2120821
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">199
+</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="n"/>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">970
@@ -2209,13 +2414,14 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">2257
+</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2232,25 +2438,37 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="n"/>
+          <t xml:space="preserve">96480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="n"/>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
@@ -2274,7 +2492,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23269
+          <t xml:space="preserve">230691
 </t>
         </is>
       </c>
@@ -2286,31 +2504,37 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">643
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2957
+          <t xml:space="preserve">957
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1954819
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1397
+</t>
+        </is>
+      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -2322,36 +2546,37 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1669
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">706
+</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194910
+          <t xml:space="preserve">4818
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
+          <t xml:space="preserve">11157
 </t>
         </is>
       </c>
@@ -2375,35 +2600,37 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">558
+</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t xml:space="preserve">11004
+</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
+          <t xml:space="preserve">909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9290
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2421,35 +2648,38 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t xml:space="preserve">48141
+</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2592
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11191
+          <t xml:space="preserve">1971
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18241
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t xml:space="preserve">98
+</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2460,10 +2690,16 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="n"/>
+          <t xml:space="preserve">2164
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1139
@@ -2472,20 +2708,25 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="n"/>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2497,7 +2738,8 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2508,42 +2750,43 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5626
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8980
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2974
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -2561,13 +2804,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3357
+          <t xml:space="preserve">9557
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">2009
 </t>
         </is>
       </c>
@@ -2579,54 +2822,79 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">8191
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="n"/>
+          <t xml:space="preserve">11822
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">9809
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2638,42 +2906,44 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">2106
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">680
+</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2690,30 +2960,31 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">257
+</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111626
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">11993
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2723,29 +2994,40 @@
 </t>
         </is>
       </c>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">1642
+</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="n"/>
+          <t xml:space="preserve">2108
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -2757,7 +3039,8 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t xml:space="preserve">243
+</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
@@ -2768,37 +3051,43 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1794
+</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
-</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">361
+</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">11995
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">1985
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
@@ -2822,59 +3111,71 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4949
-</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t xml:space="preserve">14949
+</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112494
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">11958
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">3
+</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="n"/>
+          <t xml:space="preserve">1124
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">280
@@ -2883,13 +3184,14 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t xml:space="preserve">1035
+</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
@@ -2904,34 +3206,45 @@
 </t>
         </is>
       </c>
-      <c r="T20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1880
+</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">2588
+</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -2949,48 +3262,49 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
+          <t xml:space="preserve">3713
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2036
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">8916080
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">1198
+</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11796
+          <t xml:space="preserve">1956
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2888
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3008,20 +3322,25 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n"/>
+          <t xml:space="preserve">1163
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1887
+</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">18080
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -3039,26 +3358,31 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="n"/>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">809
+</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11694
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -3068,7 +3392,12 @@
 </t>
         </is>
       </c>
-      <c r="Y21" s="2" t="n"/>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
       <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
@@ -3090,97 +3419,110 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t xml:space="preserve">2258
+</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21132
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">127
 </t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1106
-</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1195
-</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1129
-</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1214
+</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr"/>
+          <t xml:space="preserve">016
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1046
+</t>
+        </is>
+      </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">18 7
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3192,7 +3534,8 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3201,7 +3544,12 @@
 </t>
         </is>
       </c>
-      <c r="Z22" s="2" t="n"/>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3228,18 +3576,19 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11614
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -3251,13 +3600,13 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3269,83 +3618,91 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">2071
+</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="n"/>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1
+</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11136
+          <t xml:space="preserve">115136
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t xml:space="preserve">915
+</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23280
+          <t xml:space="preserve">3280
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12198
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1863
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">9389
 </t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
+          <t xml:space="preserve">4298
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">11963
 </t>
         </is>
       </c>
@@ -3363,30 +3720,40 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4379 18
+          <t xml:space="preserve">49729
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10256
+          <t xml:space="preserve">0256
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n"/>
+          <t xml:space="preserve">1134
+</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6215659
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="n"/>
+          <t xml:space="preserve">1234
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1085
+</t>
+        </is>
+      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22
@@ -3395,14 +3762,20 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">597
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 4
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3411,7 +3784,12 @@
 </t>
         </is>
       </c>
-      <c r="N24" s="2" t="n"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">978
@@ -3420,24 +3798,31 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2399
+          <t xml:space="preserve">2919
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="n"/>
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -3449,14 +3834,19 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11894
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="n"/>
+          <t xml:space="preserve">1894
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1731
+</t>
+        </is>
+      </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188812
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -3466,7 +3856,12 @@
 </t>
         </is>
       </c>
-      <c r="Z24" s="2" t="n"/>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3481,91 +3876,97 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
+          <t xml:space="preserve">2536
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">11539
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28726
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">121356
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
+          <t xml:space="preserve">1962
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
-</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1121
+</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -3577,31 +3978,43 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="n"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+</t>
+        </is>
+      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1719
+</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1220
+</t>
+        </is>
+      </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3619,7 +4032,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2583
+          <t xml:space="preserve">2683
 </t>
         </is>
       </c>
@@ -3631,19 +4044,19 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -3661,44 +4074,55 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="n"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="n"/>
+          <t xml:space="preserve">11158
+</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">888080
+</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -3710,13 +4134,13 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9318
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3728,25 +4152,25 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0153
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3764,81 +4188,98 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5358
+          <t xml:space="preserve">93517
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">013125
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20916
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
+          <t xml:space="preserve">0116
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1117
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">16
 </t>
         </is>
       </c>
-      <c r="K27" s="2" t="n"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11835
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="n"/>
+          <t xml:space="preserve">2258
+</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3861,7 +4302,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -3871,10 +4312,15 @@
 </t>
         </is>
       </c>
-      <c r="X27" s="2" t="n"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3898,7 +4344,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
@@ -3916,7 +4362,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3928,50 +4374,68 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n"/>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8075
+</t>
+        </is>
+      </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">03
+</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -3982,13 +4446,13 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4000,7 +4464,8 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">1170
+</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
@@ -4047,66 +4512,78 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="n"/>
+          <t xml:space="preserve">20185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11122
-</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">13
+</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t xml:space="preserve">1150
+</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9910
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4116,10 +4593,15 @@
 </t>
         </is>
       </c>
-      <c r="S29" s="2" t="n"/>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8561
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
@@ -4131,31 +4613,31 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119910
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4191,19 +4673,19 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">943
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15449
+          <t xml:space="preserve">6499
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16294
+          <t xml:space="preserve">629
 </t>
         </is>
       </c>
@@ -4215,38 +4697,49 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1769
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
+          <t xml:space="preserve">749
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">745
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4449244</t>
+          <t xml:space="preserve">4910
+</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2121
+          <t xml:space="preserve">4121
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
+          <t xml:space="preserve">9989
 </t>
         </is>
       </c>
@@ -4258,43 +4751,50 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94138
+          <t xml:space="preserve">41351
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">857
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr"/>
+          <t xml:space="preserve">8294
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9220
+          <t xml:space="preserve">65480
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4317,7 +4817,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4335,47 +4835,56 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1125
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">084
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1150
 </t>
         </is>
       </c>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1199
+</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">14544
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">024
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4386,45 +4895,40 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1078
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81154
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>02</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">180101
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1063
-</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -4433,7 +4937,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -4457,66 +4961,73 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2579
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128213
+          <t xml:space="preserve">1810
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">829
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>793</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7196
+          <t xml:space="preserve">2116
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
+          <t xml:space="preserve">751
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -4532,24 +5043,54 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="2" t="n"/>
-      <c r="T32" s="2" t="n"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr"/>
-      <c r="X32" s="2" t="n"/>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1162
+</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11817
+</t>
+        </is>
+      </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="2" t="n"/>
+          <t xml:space="preserve">1960
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>21</t>
@@ -4576,7 +5117,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -4588,48 +5129,55 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">110080
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1115
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">1049
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110972
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">9628
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4641,49 +5189,61 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201912
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="n"/>
-      <c r="T33" s="2" t="n"/>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718
+</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2916
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1165
+</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19800
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4701,18 +5261,19 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t xml:space="preserve">2114
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">11972
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">11597
 </t>
         </is>
       </c>
@@ -4724,98 +5285,121 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">946
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11452
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1142
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">003
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">985
+</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">52
+</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1969
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">169
 </t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="n"/>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>432</t>
+          <t xml:space="preserve">152
+</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4839,7 +5423,8 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -4850,7 +5435,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">21818
 </t>
         </is>
       </c>
@@ -4868,12 +5453,13 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4891,13 +5477,13 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212818
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1141
 </t>
         </is>
       </c>
@@ -4915,22 +5501,28 @@
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -4939,29 +5531,31 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2840
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4985,42 +5579,43 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">17138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t xml:space="preserve">10995
+</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">11059
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">935
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5032,49 +5627,61 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11150
+          <t xml:space="preserve">0120
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11616
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5086,24 +5693,25 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t xml:space="preserve">172
+</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5121,7 +5729,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>197824</t>
+          <t xml:space="preserve">20782
+</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5132,30 +5741,31 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">8194
 </t>
         </is>
       </c>
@@ -5167,76 +5777,79 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1501
+          <t xml:space="preserve">50717
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16815
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1676
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t xml:space="preserve">1010
+</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1899
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3821914</t>
+          <t xml:space="preserve">3809
+</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2332
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t xml:space="preserve">900
+</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1816
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -5248,13 +5861,14 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">4299
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5275,81 +5889,99 @@
 </t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">10251
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1913
+          <t xml:space="preserve">1615
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1137
+</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t xml:space="preserve">1135
+</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t xml:space="preserve">202
+</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t xml:space="preserve">11170
+</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11720
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
@@ -5361,32 +5993,32 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181014
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="n"/>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01846
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">812
 </t>
         </is>
       </c>
@@ -5404,7 +6036,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
+          <t xml:space="preserve">6641
 </t>
         </is>
       </c>
@@ -5416,13 +6048,13 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5434,32 +6066,43 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n"/>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">8 1
 </t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2193
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121202
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5471,57 +6114,67 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012
+          <t xml:space="preserve">012
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1505
+          <t xml:space="preserve">15210
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V39" s="2" t="inlineStr"/>
-      <c r="W39" s="2" t="n"/>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1275
+</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0625
+</t>
+        </is>
+      </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1988
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5545,13 +6198,13 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -5563,7 +6216,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -5582,13 +6235,13 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
@@ -5600,7 +6253,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -5612,30 +6265,31 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">088
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0488
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
@@ -5647,30 +6301,31 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">173
+</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1628
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -5688,7 +6343,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7943
+          <t xml:space="preserve">6943
 </t>
         </is>
       </c>
@@ -5698,104 +6353,135 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 37
+</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">1053
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11208
-</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">12935
+</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">581
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">470
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 1 4
+          <t xml:space="preserve">813
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -5813,7 +6499,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
@@ -5825,37 +6511,37 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24709
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11224
+          <t xml:space="preserve">11817
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11605
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -5867,18 +6553,28 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n"/>
+          <t xml:space="preserve">01107
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">04
@@ -5887,7 +6583,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5899,19 +6595,19 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9490
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">1474
 </t>
         </is>
       </c>
@@ -5923,25 +6619,25 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11686
+          <t xml:space="preserve">11610
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -5959,65 +6655,78 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
+          <t xml:space="preserve">6094
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">16 279
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">294
+</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="n"/>
+          <t xml:space="preserve">1130
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110219
+</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">248
@@ -6038,42 +6747,43 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
+</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">399
 </t>
         </is>
       </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7298
-</t>
-        </is>
-      </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">2119
 </t>
         </is>
       </c>
@@ -6089,7 +6799,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -6133,18 +6848,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t xml:space="preserve">1319
+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">036
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
@@ -6162,7 +6878,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
@@ -6174,13 +6890,13 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">0800
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3564
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
@@ -6192,77 +6908,79 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">619
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t xml:space="preserve">4900
+</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">2125
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11089
+          <t xml:space="preserve">1089
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">837
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10609
+          <t xml:space="preserve">6580
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028 1
+          <t xml:space="preserve">3828
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">2815
 </t>
         </is>
       </c>
@@ -6286,74 +7004,85 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t xml:space="preserve">11015
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">11815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15034
+          <t xml:space="preserve">12004
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111110
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11113
+          <t xml:space="preserve">112198
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">11119
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="n"/>
+          <t xml:space="preserve">1351
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9001
+</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0241
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2353
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6363,8 +7092,18 @@
 </t>
         </is>
       </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="n"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">598
+</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">18654
@@ -6373,24 +7112,29 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1166
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">215416
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n"/>
       <c r="X46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
         </is>
       </c>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="n"/>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">692
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1814
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -686,7 +686,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -698,25 +698,25 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8202
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8197
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1893
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -728,7 +728,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -746,7 +746,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -782,7 +782,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">146495
 </t>
         </is>
       </c>
@@ -794,13 +794,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1140
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -830,7 +830,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -854,7 +854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">958
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -896,13 +896,13 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -920,8 +920,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -944,19 +943,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -968,7 +967,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -986,25 +985,25 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215621
+          <t xml:space="preserve">12561
 </t>
         </is>
       </c>
@@ -1014,12 +1013,7 @@
 </t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+      <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">222
@@ -1064,7 +1058,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
@@ -1076,7 +1070,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -1094,7 +1088,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2552
+          <t xml:space="preserve">3537
 </t>
         </is>
       </c>
@@ -1112,7 +1106,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -1148,7 +1142,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -1166,7 +1160,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1190,19 +1184,19 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1250,7 +1244,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3778
+          <t xml:space="preserve">3779
 </t>
         </is>
       </c>
@@ -1262,13 +1256,13 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -1292,7 +1286,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -1304,31 +1298,31 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1131
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1364,13 +1358,13 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -1418,7 +1412,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">713
 </t>
         </is>
       </c>
@@ -1430,7 +1424,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -1446,15 +1440,10 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12819
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
@@ -1466,31 +1455,31 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">891
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4238
+          <t xml:space="preserve">4220
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1033
 </t>
         </is>
       </c>
@@ -1502,13 +1491,13 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9856
+          <t xml:space="preserve">92856
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09101
+          <t xml:space="preserve">8911
 </t>
         </is>
       </c>
@@ -1532,19 +1521,19 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9498
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942908
+          <t xml:space="preserve">94298
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -1574,7 +1563,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -1586,13 +1575,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -1604,31 +1593,31 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1640,7 +1629,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83 8
+          <t xml:space="preserve">6 2
 </t>
         </is>
       </c>
@@ -1664,24 +1653,25 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -1723,19 +1713,19 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">1333
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -1765,25 +1755,25 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">2 316
 </t>
         </is>
       </c>
@@ -1795,13 +1785,13 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">1023
 </t>
         </is>
       </c>
@@ -1813,7 +1803,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2899
 </t>
         </is>
       </c>
@@ -1825,31 +1815,31 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2184
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1873,7 +1863,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5811
+          <t xml:space="preserve">5011
 </t>
         </is>
       </c>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2539
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -1897,13 +1887,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">018
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">01100
 </t>
         </is>
       </c>
@@ -1913,12 +1903,7 @@
 </t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1121
-</t>
-        </is>
-      </c>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1927,7 +1912,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">1145
 </t>
         </is>
       </c>
@@ -1939,19 +1924,19 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -1963,19 +1948,19 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141046
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -2011,7 +1996,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -2029,7 +2014,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5556
+          <t xml:space="preserve">1556
 </t>
         </is>
       </c>
@@ -2041,19 +2026,19 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2216
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -2083,19 +2068,19 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8196
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -2107,7 +2092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2125,7 +2110,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -2135,7 +2120,12 @@
 </t>
         </is>
       </c>
-      <c r="U13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">208
@@ -2144,7 +2134,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -2162,7 +2152,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2180,13 +2170,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0318
+          <t xml:space="preserve">0329
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -2204,7 +2194,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2045
+          <t xml:space="preserve">0145
 </t>
         </is>
       </c>
@@ -2222,13 +2212,13 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2246,7 +2236,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
+          <t xml:space="preserve">1943
 </t>
         </is>
       </c>
@@ -2282,13 +2272,13 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2300,13 +2290,13 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
@@ -2336,7 +2326,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
+          <t xml:space="preserve">4545
 </t>
         </is>
       </c>
@@ -2348,61 +2338,61 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1149
 </t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2120821
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -2420,7 +2410,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -2438,13 +2428,13 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96480
+          <t xml:space="preserve">2480
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -2456,19 +2446,19 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -2492,7 +2482,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230691
+          <t xml:space="preserve">23069
 </t>
         </is>
       </c>
@@ -2504,7 +2494,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">643
+          <t xml:space="preserve">6553
 </t>
         </is>
       </c>
@@ -2522,37 +2512,37 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">589
+          <t xml:space="preserve">489
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1349
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">669
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2564,19 +2554,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4818
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11157
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -2606,7 +2596,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11004
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
@@ -2618,13 +2608,13 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">94210
 </t>
         </is>
       </c>
@@ -2648,13 +2638,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48141
+          <t xml:space="preserve">08141
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2666,13 +2656,13 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1971
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
@@ -2690,19 +2680,18 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -2714,13 +2703,13 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -2744,7 +2733,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1183
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2786,7 +2775,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2810,7 +2799,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -2822,37 +2811,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -2864,31 +2848,31 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11822
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9809
+          <t xml:space="preserve">9828
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
@@ -2906,31 +2890,31 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2106
+          <t xml:space="preserve">2102
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">16 7
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -2942,7 +2926,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -2960,7 +2944,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -2972,13 +2956,13 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1630
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11993
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -3002,7 +2986,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3014,20 +2998,25 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1642
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2108
-</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
@@ -3039,7 +3028,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3051,7 +3040,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3063,25 +3052,25 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11995
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">2889
 </t>
         </is>
       </c>
@@ -3111,25 +3100,25 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14949
+          <t xml:space="preserve">14979
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11958
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -3147,31 +3136,31 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -3184,13 +3173,13 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1035
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -3202,13 +3191,13 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1167
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1880
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -3220,13 +3209,13 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">1912
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2588
+          <t xml:space="preserve">1177
 </t>
         </is>
       </c>
@@ -3238,7 +3227,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -3268,13 +3257,13 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8916080
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -3286,19 +3275,19 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1956
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3322,7 +3311,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
@@ -3334,7 +3323,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18080
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -3358,7 +3347,7 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3370,7 +3359,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -3382,19 +3371,19 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3419,26 +3408,25 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3453,7 +3441,12 @@
 </t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">517
@@ -3462,19 +3455,19 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">11209
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3486,19 +3479,19 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">016
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1046
+          <t xml:space="preserve">12246
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 7
+          <t xml:space="preserve">18 54
 </t>
         </is>
       </c>
@@ -3510,13 +3503,13 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3534,7 +3527,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -3570,7 +3563,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11285
+          <t xml:space="preserve">11284
 </t>
         </is>
       </c>
@@ -3588,7 +3581,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -3618,19 +3611,19 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2071
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">696
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
@@ -3640,39 +3633,28 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+      <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115136
+          <t xml:space="preserve">1156
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">915
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">9185
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3280
-</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
+          <t xml:space="preserve">0498
 </t>
         </is>
       </c>
@@ -3684,13 +3666,13 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9389
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -3702,7 +3684,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11963
+          <t xml:space="preserve">1983
 </t>
         </is>
       </c>
@@ -3720,13 +3702,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49729
+          <t xml:space="preserve">49129
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0256
+          <t xml:space="preserve">2356
 </t>
         </is>
       </c>
@@ -3750,7 +3732,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1085
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -3762,19 +3744,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">597
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 4
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">371
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3786,7 +3763,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3798,19 +3775,19 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">0944
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2919
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -3822,7 +3799,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3840,7 +3817,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1731
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3858,7 +3835,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3876,19 +3853,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2536
+          <t xml:space="preserve">2236
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">23 1
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11539
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -3900,19 +3877,18 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121356
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3924,13 +3900,13 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1962
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3942,49 +3918,49 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -3996,7 +3972,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -4008,13 +3984,13 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">9208
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -4050,40 +4026,35 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">177
 </t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">158
@@ -4092,7 +4063,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11158
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
@@ -4104,19 +4075,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888080
+          <t xml:space="preserve">9088
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4134,7 +4105,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -4152,19 +4123,19 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">070
 </t>
         </is>
       </c>
@@ -4188,7 +4159,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93517
+          <t xml:space="preserve">4358
 </t>
         </is>
       </c>
@@ -4212,19 +4183,19 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">013125
+          <t xml:space="preserve">01312
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4242,19 +4213,19 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">1088
 </t>
         </is>
       </c>
@@ -4266,13 +4237,13 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -4288,12 +4259,7 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">870
-</t>
-        </is>
-      </c>
+      <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -4302,7 +4268,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4320,7 +4286,7 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -4344,7 +4310,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3313
 </t>
         </is>
       </c>
@@ -4362,25 +4328,25 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8075
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -4404,7 +4370,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -4446,13 +4412,13 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -4506,28 +4472,23 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20185
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">122
@@ -4554,7 +4515,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>37</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4583,7 +4544,7 @@
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -4619,13 +4580,13 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -4637,7 +4598,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4679,7 +4640,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6499
+          <t xml:space="preserve">6459
 </t>
         </is>
       </c>
@@ -4697,7 +4658,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4709,37 +4670,32 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">745
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4910
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4121
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4918
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9989
+          <t xml:space="preserve">999
 </t>
         </is>
       </c>
@@ -4751,13 +4707,13 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41351
+          <t xml:space="preserve">4131
 </t>
         </is>
       </c>
@@ -4769,31 +4725,31 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8294
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65480
+          <t xml:space="preserve">942280
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -4823,7 +4779,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -4841,25 +4797,25 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
+          <t xml:space="preserve">0815
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4878,15 +4834,11 @@
       <c r="N31" s="2" t="n"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14544
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16441
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4895,7 +4847,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1078
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -4907,24 +4859,25 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">92116
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t xml:space="preserve">044
+</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180101
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
@@ -4937,7 +4890,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4961,13 +4914,13 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -4985,7 +4938,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">879
 </t>
         </is>
       </c>
@@ -4997,34 +4950,39 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>291</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">751
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">82
@@ -5039,13 +4997,13 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -5057,13 +5015,13 @@
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">1166
 </t>
         </is>
       </c>
@@ -5075,19 +5033,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -5117,7 +5075,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
+          <t xml:space="preserve">1137
 </t>
         </is>
       </c>
@@ -5129,13 +5087,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110080
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">2115
 </t>
         </is>
       </c>
@@ -5159,19 +5117,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1049
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9628
+          <t xml:space="preserve">1601
 </t>
         </is>
       </c>
@@ -5189,61 +5147,61 @@
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
+          <t xml:space="preserve">0165
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -5267,13 +5225,13 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11972
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11597
+          <t xml:space="preserve">15719
 </t>
         </is>
       </c>
@@ -5285,7 +5243,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5303,37 +5261,32 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">003
+          <t xml:space="preserve">023
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">52
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">157
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5345,7 +5298,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5363,7 +5316,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -5375,7 +5328,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
@@ -5387,13 +5340,13 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
@@ -5417,13 +5370,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5435,13 +5388,13 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21818
+          <t xml:space="preserve">2181
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -5459,7 +5412,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5481,12 +5434,7 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-</t>
-        </is>
-      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5495,25 +5443,25 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
@@ -5531,7 +5479,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -5543,7 +5491,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5579,19 +5527,19 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10995
+          <t xml:space="preserve">0195
 </t>
         </is>
       </c>
@@ -5603,13 +5551,13 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11059
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -5627,7 +5575,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0120
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
@@ -5639,25 +5587,25 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8708
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -5675,19 +5623,19 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">801
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5699,13 +5647,13 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
@@ -5765,7 +5713,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194
+          <t xml:space="preserve">1814
 </t>
         </is>
       </c>
@@ -5777,7 +5725,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50717
+          <t xml:space="preserve">507
 </t>
         </is>
       </c>
@@ -5789,13 +5737,13 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">676
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5807,7 +5755,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5825,19 +5773,19 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
+          <t xml:space="preserve">38019
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -5861,13 +5809,13 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4299
+          <t xml:space="preserve">4222
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -5885,14 +5833,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4956
+          <t xml:space="preserve">4156
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
-</t>
+          <t>837</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5903,25 +5850,25 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10251
+          <t xml:space="preserve">10351
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1615
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">11702
 </t>
         </is>
       </c>
@@ -5933,7 +5880,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5951,19 +5898,19 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">02 4
 </t>
         </is>
       </c>
@@ -5975,13 +5922,13 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
@@ -5993,13 +5940,13 @@
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1 6 1
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -6012,13 +5959,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">812
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -6036,7 +5983,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6641
+          <t xml:space="preserve">6244
 </t>
         </is>
       </c>
@@ -6048,7 +5995,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -6084,13 +6031,12 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 1
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6102,14 +6048,13 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -6120,7 +6065,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -6132,25 +6077,25 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15210
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -6162,13 +6107,13 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
@@ -6216,95 +6161,99 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">489
+</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">253
 </t>
         </is>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">088
-</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">489
-</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">173
@@ -6325,7 +6274,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6343,25 +6292,25 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6943
+          <t xml:space="preserve">6993
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">1871
 </t>
         </is>
       </c>
@@ -6371,12 +6320,7 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 37
-</t>
-        </is>
-      </c>
+      <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">47
@@ -6385,7 +6329,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -6397,19 +6341,19 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1053
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6427,61 +6371,61 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12935
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1722
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">581
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">470
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">813
+          <t xml:space="preserve">26417
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -6499,7 +6443,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">6088
 </t>
         </is>
       </c>
@@ -6511,7 +6455,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6523,25 +6467,25 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">538
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">940
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6553,25 +6497,25 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01107
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6583,7 +6527,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">2617
 </t>
         </is>
       </c>
@@ -6607,7 +6551,7 @@
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -6631,13 +6575,13 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -6655,7 +6599,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6094
+          <t xml:space="preserve">50494
 </t>
         </is>
       </c>
@@ -6674,7 +6618,7 @@
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 279
+          <t xml:space="preserve">1 279
 </t>
         </is>
       </c>
@@ -6710,20 +6654,20 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110219
+          <t xml:space="preserve">11227
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6747,13 +6691,13 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6765,25 +6709,25 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2119
+          <t xml:space="preserve">2109
 </t>
         </is>
       </c>
@@ -6854,13 +6798,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">536
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6884,19 +6828,19 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">364
 </t>
         </is>
       </c>
@@ -6914,13 +6858,13 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
@@ -6938,20 +6882,19 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125
+          <t xml:space="preserve">21725
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6962,25 +6905,25 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">837
+          <t xml:space="preserve">881
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6580
+          <t xml:space="preserve">681
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3828
+          <t xml:space="preserve">3028
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2815
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -7010,25 +6953,25 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11015
+          <t xml:space="preserve">11014
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12004
+          <t xml:space="preserve">810154
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -7046,31 +6989,31 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111110
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112198
+          <t xml:space="preserve">112138
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11119
+          <t xml:space="preserve">11019
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1351
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -7088,7 +7031,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
@@ -7106,13 +7049,13 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18654
+          <t xml:space="preserve">13654
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215416
+          <t xml:space="preserve">218416
 </t>
         </is>
       </c>
@@ -7125,13 +7068,13 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -656,7 +656,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -692,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -704,13 +704,13 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -728,7 +728,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -740,7 +740,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">0178
 </t>
         </is>
       </c>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -782,13 +782,13 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146495
+          <t xml:space="preserve">4645
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -854,13 +854,13 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -872,13 +872,13 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -902,7 +902,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -920,7 +920,8 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">66
+</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -943,37 +944,37 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -991,19 +992,19 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1942
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12561
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1028,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1058,7 +1059,7 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1070,7 +1071,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -1088,7 +1089,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3537
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
@@ -1160,7 +1161,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -1178,7 +1179,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1190,7 +1191,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -1214,7 +1215,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -1226,7 +1227,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
@@ -1268,7 +1269,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
@@ -1310,13 +1311,13 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1346,7 +1347,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -1400,7 +1401,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18252
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
@@ -1412,8 +1413,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">713
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1440,7 +1440,12 @@
 </t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">917
+</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">289
@@ -1455,25 +1460,25 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1491,13 +1496,13 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92856
+          <t xml:space="preserve">1986
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8911
+          <t xml:space="preserve">8918
 </t>
         </is>
       </c>
@@ -1509,13 +1514,13 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">955
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8712
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -1527,13 +1532,13 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94298
+          <t xml:space="preserve">94290
 </t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -1551,7 +1556,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36501
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -1575,7 +1580,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1599,25 +1604,25 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -1629,13 +1634,13 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 2
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -1653,19 +1658,19 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">11914
 </t>
         </is>
       </c>
@@ -1707,25 +1712,25 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3296
+          <t xml:space="preserve">3246
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1333
+          <t xml:space="preserve">753
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -1749,103 +1754,103 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1179
+</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11228
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2136
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1023
+</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12204
+</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">174
 </t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 316
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1023
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2899
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">720
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">11586
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1863,13 +1868,13 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5011
+          <t xml:space="preserve">5111
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -1881,7 +1886,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1893,17 +1898,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01100
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -1912,55 +1922,55 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1145
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -1990,13 +2000,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">2810
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2014,7 +2024,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
@@ -2026,7 +2036,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
@@ -2038,7 +2048,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -2062,25 +2072,25 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -2092,7 +2102,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
@@ -2104,19 +2114,18 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">18668
 </t>
         </is>
       </c>
@@ -2146,7 +2155,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
@@ -2170,7 +2179,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0329
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -2188,13 +2197,13 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0145
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2224,19 +2233,19 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1125
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1943
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -2248,7 +2257,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2272,13 +2281,13 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -2290,19 +2299,19 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2326,7 +2335,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4545
+          <t xml:space="preserve">4845
 </t>
         </is>
       </c>
@@ -2350,7 +2359,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -2362,19 +2371,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2392,13 +2401,13 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -2428,7 +2437,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2480
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
@@ -2452,7 +2461,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2464,7 +2473,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2494,7 +2503,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6553
+          <t xml:space="preserve">652
 </t>
         </is>
       </c>
@@ -2506,7 +2515,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
@@ -2524,13 +2533,13 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1349
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2542,31 +2551,25 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>456</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
-</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4320
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1157
 </t>
         </is>
       </c>
@@ -2590,31 +2593,31 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">2558
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">909
+          <t xml:space="preserve">1909
 </t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -2638,31 +2641,31 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08141
+          <t xml:space="preserve">4614
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
+          <t xml:space="preserve">21124
 </t>
         </is>
       </c>
@@ -2680,18 +2683,19 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">1139
 </t>
         </is>
       </c>
@@ -2709,7 +2713,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -2727,7 +2731,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2745,13 +2749,13 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">2014
 </t>
         </is>
       </c>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
@@ -2793,13 +2797,13 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9557
+          <t xml:space="preserve">3557
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2228
 </t>
         </is>
       </c>
@@ -2823,14 +2827,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1126
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2848,19 +2857,19 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9828
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2872,7 +2881,7 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12168
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
@@ -2890,25 +2899,25 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">1740
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2102
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 7
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -2956,7 +2965,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1630
+          <t xml:space="preserve">2130
 </t>
         </is>
       </c>
@@ -2968,13 +2977,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
@@ -2986,13 +2995,13 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">017
 </t>
         </is>
       </c>
@@ -3004,20 +3013,19 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3028,7 +3036,7 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3040,7 +3048,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1794
 </t>
         </is>
       </c>
@@ -3052,13 +3060,13 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -3070,7 +3078,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3100,7 +3108,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14979
+          <t xml:space="preserve">14179
 </t>
         </is>
       </c>
@@ -3112,7 +3120,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">11254
 </t>
         </is>
       </c>
@@ -3164,11 +3172,15 @@
 </t>
         </is>
       </c>
-      <c r="N20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3179,7 +3191,7 @@
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -3197,43 +3209,43 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">8 0
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1912
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3251,7 +3263,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713
+          <t xml:space="preserve">3793
 </t>
         </is>
       </c>
@@ -3263,7 +3275,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">0140
 </t>
         </is>
       </c>
@@ -3275,7 +3287,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -3287,7 +3299,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -3299,7 +3311,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
@@ -3311,13 +3323,13 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -3341,7 +3353,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -3359,7 +3371,7 @@
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -3371,23 +3383,28 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">9181
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3414,19 +3431,20 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">11132
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3461,7 +3479,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11209
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3473,43 +3491,43 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">2970
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 54
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3527,7 +3545,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -3563,7 +3581,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11284
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -3581,7 +3599,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">614
 </t>
         </is>
       </c>
@@ -3593,8 +3611,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>013</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -3605,13 +3622,13 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
@@ -3623,8 +3640,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3633,7 +3649,12 @@
 </t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1156
@@ -3642,19 +3663,20 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">1915
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t xml:space="preserve">2328
+</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0498
+          <t xml:space="preserve">1498
 </t>
         </is>
       </c>
@@ -3672,7 +3694,7 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
@@ -3684,7 +3706,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1983
+          <t xml:space="preserve">1163
 </t>
         </is>
       </c>
@@ -3702,13 +3724,13 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49129
+          <t xml:space="preserve">4179
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2356
+          <t xml:space="preserve">0236
 </t>
         </is>
       </c>
@@ -3720,19 +3742,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1108
 </t>
         </is>
       </c>
@@ -3744,14 +3766,14 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -3763,7 +3785,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -3775,7 +3797,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0944
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3799,7 +3821,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -3811,7 +3833,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
@@ -3823,7 +3845,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -3835,7 +3857,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3853,19 +3875,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2236
+          <t xml:space="preserve">2336
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23 1
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
@@ -3877,7 +3899,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">76
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3888,7 +3911,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">006
 </t>
         </is>
       </c>
@@ -3900,25 +3923,25 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">1160
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3930,13 +3953,13 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3960,37 +3983,36 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1719
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9208
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4008,7 +4030,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2683
+          <t xml:space="preserve">2283
 </t>
         </is>
       </c>
@@ -4032,13 +4054,13 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4048,7 +4070,12 @@
 </t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">177
@@ -4069,19 +4096,19 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9088
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -4093,19 +4120,19 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4123,28 +4150,18 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">153
+</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">070
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="n"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -4159,7 +4176,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4358
+          <t xml:space="preserve">4356
 </t>
         </is>
       </c>
@@ -4183,7 +4200,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01312
+          <t xml:space="preserve">10122
 </t>
         </is>
       </c>
@@ -4195,7 +4212,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4213,19 +4230,19 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">1735
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1088
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -4243,7 +4260,7 @@
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -4259,16 +4276,20 @@
 </t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">879
+</t>
+        </is>
+      </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -4328,7 +4349,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4346,7 +4367,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4370,7 +4391,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
@@ -4382,7 +4403,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -4406,19 +4427,19 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4466,7 +4487,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">3097
 </t>
         </is>
       </c>
@@ -4478,20 +4499,25 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -4515,7 +4541,8 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37</t>
+          <t xml:space="preserve">1137
+</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4526,19 +4553,18 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>744</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4556,13 +4582,13 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -4574,19 +4600,19 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -4616,7 +4642,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15699
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -4640,13 +4666,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6459
+          <t xml:space="preserve">449
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">629
+          <t xml:space="preserve">624
 </t>
         </is>
       </c>
@@ -4658,19 +4684,19 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">76 9
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">749
 </t>
         </is>
       </c>
@@ -4682,14 +4708,13 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr"/>
@@ -4707,7 +4732,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
@@ -4731,25 +4756,25 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">942280
+          <t xml:space="preserve">94280
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -4773,13 +4798,13 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">1144
 </t>
         </is>
       </c>
@@ -4803,7 +4828,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0815
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4813,12 +4838,7 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1150
@@ -4827,18 +4847,28 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="n"/>
+          <t xml:space="preserve">1149
+</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16441
-</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">604
+</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">001
+</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">199
@@ -4847,7 +4877,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
@@ -4859,19 +4889,19 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92116
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">17 0
 </t>
         </is>
       </c>
@@ -4881,7 +4911,12 @@
 </t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">950
@@ -4890,7 +4925,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4914,66 +4949,67 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2207
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1810
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t xml:space="preserve">391
+</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">5716
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4991,34 +5027,24 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1195
+</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">80
 </t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
+      <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1166
@@ -5033,19 +5059,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -5081,7 +5107,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -5093,19 +5119,19 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5117,19 +5143,19 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1601
+          <t xml:space="preserve">191619
 </t>
         </is>
       </c>
@@ -5159,49 +5185,49 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">718
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">28809
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5225,13 +5251,13 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15719
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -5243,13 +5269,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1142
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -5261,13 +5287,13 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">023
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5277,7 +5303,12 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5 1
+</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">170
@@ -5286,7 +5317,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5298,7 +5329,7 @@
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5310,13 +5341,13 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
@@ -5334,7 +5365,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
@@ -5346,7 +5377,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">1900
 </t>
         </is>
       </c>
@@ -5370,25 +5401,25 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2181
+          <t xml:space="preserve">1181
 </t>
         </is>
       </c>
@@ -5400,7 +5431,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5430,11 +5461,16 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1123
+</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">980
@@ -5443,13 +5479,13 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -5461,13 +5497,13 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1 1 9
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">608
 </t>
         </is>
       </c>
@@ -5479,31 +5515,31 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1284
 </t>
         </is>
       </c>
@@ -5533,25 +5569,25 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5575,25 +5611,25 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
@@ -5605,7 +5641,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5623,13 +5659,13 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">801
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5653,13 +5689,13 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -5683,67 +5719,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">661
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">3523
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1814
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">507
+          <t xml:space="preserve">5079
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">676
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -5755,7 +5791,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -5767,7 +5803,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">599
 </t>
         </is>
       </c>
@@ -5779,7 +5815,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38019
+          <t xml:space="preserve">3809
 </t>
         </is>
       </c>
@@ -5791,7 +5827,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">700
 </t>
         </is>
       </c>
@@ -5809,16 +5845,11 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4222
-</t>
-        </is>
-      </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4298
+</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -5839,7 +5870,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5856,31 +5888,31 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10351
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11702
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -5892,13 +5924,13 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -5910,7 +5942,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02 4
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
@@ -5922,50 +5954,55 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">762
+</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1176
 </t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">762
-</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 6 1
-</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="W38" s="2" t="n"/>
-      <c r="X38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -5983,7 +6020,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6244
+          <t xml:space="preserve">6243
 </t>
         </is>
       </c>
@@ -5995,7 +6032,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -6019,24 +6056,25 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -6048,13 +6086,14 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t xml:space="preserve">910
+</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -6065,19 +6104,19 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -6095,19 +6134,19 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2715
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0625
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6149,7 +6188,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -6161,13 +6200,14 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">153
+</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -6214,7 +6254,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -6232,13 +6272,13 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
+          <t xml:space="preserve">19488
 </t>
         </is>
       </c>
@@ -6250,7 +6290,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6274,7 +6314,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">2008
 </t>
         </is>
       </c>
@@ -6292,7 +6332,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6993
+          <t xml:space="preserve">6443
 </t>
         </is>
       </c>
@@ -6304,13 +6344,13 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1871
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -6321,15 +6361,10 @@
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">47
-</t>
-        </is>
-      </c>
+      <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6341,25 +6376,25 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -6377,55 +6412,55 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">081
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9470
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26417
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">2390
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -6455,31 +6490,31 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">4709
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11817
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">940
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -6491,31 +6526,31 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6527,7 +6562,7 @@
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2617
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -6537,42 +6572,37 @@
 </t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">490
+</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1168
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">490
-</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11610
-</t>
-        </is>
-      </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">610
@@ -6581,7 +6611,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6599,7 +6629,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50494
+          <t xml:space="preserve">6044
 </t>
         </is>
       </c>
@@ -6611,14 +6641,19 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 279
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -6654,20 +6689,25 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11227
-</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="n"/>
+          <t xml:space="preserve">1207
+</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6685,25 +6725,24 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>465</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">2224
 </t>
         </is>
       </c>
@@ -6715,19 +6754,19 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">91209
 </t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
+          <t xml:space="preserve">2392
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2109
+          <t xml:space="preserve">21262
 </t>
         </is>
       </c>
@@ -6792,7 +6831,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
@@ -6810,7 +6849,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
@@ -6828,43 +6867,42 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">364
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">1559
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">619
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">94980
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6882,19 +6920,20 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21725
+          <t xml:space="preserve">2825
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -6905,19 +6944,19 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">881
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">681
+          <t xml:space="preserve">106888
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3028
+          <t xml:space="preserve">23028
 </t>
         </is>
       </c>
@@ -6953,19 +6992,19 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11014
+          <t xml:space="preserve">11017
 </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810154
+          <t xml:space="preserve">1513
 </t>
         </is>
       </c>
@@ -6983,43 +7022,43 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">111119
 </t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112138
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11019
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0241
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -7031,35 +7070,40 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">585
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13654
+          <t xml:space="preserve">0654
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218416
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1166
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">160
@@ -7068,13 +7112,13 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1612
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,146 +626,122 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2891
-</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -782,146 +758,122 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4645
-</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -938,141 +890,118 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3380
-</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1942
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1089,146 +1018,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1245,146 +1150,122 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3779
-</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1131
-</t>
+          <t>151</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,14 +1282,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
-</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1418,128 +1297,107 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
-</t>
+          <t>615</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1033
-</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>899</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
-</t>
+          <t>956</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8918
-</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
-</t>
+          <t>955</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
+          <t>872</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,146 +1414,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111001</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11914
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,146 +1546,122 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3246
-</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">753
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11228
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1023
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12204
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11586
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,146 +1678,122 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2810
-</t>
+          <t>850</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,92 +1810,77 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
+          <t>4556</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -2119,50 +1890,42 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2179,146 +1942,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">711
-</t>
+          <t>711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2335,146 +2074,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4845
-</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2491,68 +2206,57 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23069
-</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
+          <t>652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">957
-</t>
+          <t>957</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">489
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">669
-</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2562,69 +2266,58 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1157
-</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
-</t>
+          <t>916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
-</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1909
-</t>
+          <t>909</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2641,146 +2334,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4614
-</t>
+          <t>514</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>848</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2797,146 +2466,122 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3557
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2228
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2953,74 +2598,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -3030,68 +2663,57 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1794
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3108,74 +2730,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11254
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -3185,68 +2795,57 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 0
-</t>
+          <t>12 0</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3263,146 +2862,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3793
-</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">809
-</t>
+          <t>809</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9181
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3419,146 +2994,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5089
-</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11132
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3575,38 +3126,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20894
-</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
-</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">614
-</t>
+          <t>614</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">539
-</t>
+          <t>539</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3616,26 +3161,22 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
-</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">696
-</t>
+          <t>696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3645,69 +3186,58 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1156
-</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1915
-</t>
+          <t>915</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2328
-</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1498
-</t>
+          <t>498</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
-</t>
+          <t>863</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3724,141 +3254,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0236
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1139
-</t>
+          <t>139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3875,128 +3386,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2336
-</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">006
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
@@ -4006,14 +3496,12 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4030,135 +3518,113 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2283
-</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z26" s="2" t="n"/>
@@ -4176,110 +3642,92 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10122
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1735
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">879
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -4289,32 +3737,27 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4331,146 +3774,122 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3313
-</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4487,68 +3906,57 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3097
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -4558,74 +3966,62 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4642,74 +4038,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>1569</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">943
-</t>
+          <t>943</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">449
-</t>
+          <t>449</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">624
-</t>
+          <t>624</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76 9
-</t>
+          <t>76 9</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">749
-</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4720,62 +4104,52 @@
       <c r="P30" s="2" t="inlineStr"/>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">999
-</t>
+          <t>994</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94280
-</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4792,141 +4166,118 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3140
-</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">604
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">001
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 0
-</t>
+          <t>17 0</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4943,136 +4294,114 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3642
-</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
+          <t>393</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5716
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5089,146 +4418,122 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>143</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191619
-</t>
+          <t>161</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28809
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5245,146 +4550,122 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
-</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 1
-</t>
+          <t>115 0</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5401,146 +4682,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1 9
-</t>
+          <t>8 9</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">608
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1284
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5557,146 +4814,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
-</t>
+          <t>718</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5713,140 +4946,117 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20782
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
-</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">661
-</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3523
-</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5079
-</t>
+          <t>501</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>771</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
-</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">599
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
-</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3809
-</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
+          <t>700</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>816</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298
-</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr"/>
@@ -5864,146 +5074,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">762
-</t>
+          <t>762</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
-</t>
+          <t>859</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6020,146 +5206,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">012
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2715
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6176,146 +5338,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6377
-</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19488
-</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>628</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6332,136 +5470,114 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6443
-</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">081
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9470
-</t>
+          <t>470</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2390
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6478,141 +5594,118 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6088
-</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4709
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
-</t>
+          <t>490</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6629,98 +5722,82 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6044
-</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -6730,44 +5807,37 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91209
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2392
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21262
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6784,8 +5854,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6825,44 +5894,37 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31195
-</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
-</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">536
-</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>775</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -6872,98 +5934,82 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
-</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1559
-</t>
+          <t>559</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94980
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
-</t>
+          <t>892</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2825
-</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1089
-</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106888
-</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23028
-</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6980,146 +6026,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2239
-</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11017
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1513
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111119
-</t>
+          <t>1111111110</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">585
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0654
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1612
-</t>
+          <t>612</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -741,7 +741,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>121</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>675</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>28</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>111001</t>
+          <t>0101</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>286</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>868</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1733,17 +1733,17 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>162</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>222</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr"/>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>993</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>982</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>07</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>185</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>192</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>980</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>154</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>262</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>183</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>71 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>122</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>93</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>169</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>180</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>191</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>159</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1168 2</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>904</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>904</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>149 1</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>81</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>916</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>144</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17 0</t>
+          <t>17 04</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>1815 0</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4334,17 +4334,17 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>323</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>880</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115 0</t>
+          <t>115 00</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>291</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>960</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>8 9</t>
+          <t>2 7 9</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>323</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>116</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3809 1</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>900</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>910</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>06</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>282</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>322</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>189</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>31195</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>260</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6009,7 +6009,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>1111111110</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>585</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/702/Midpoint_Excel_with_OCR_Results.xlsx
@@ -966,7 +966,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>377</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1719</t>
+          <t>171</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18252</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>895</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0101</t>
+          <t>210</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>158</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>208</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>511</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>301</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>760</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>998</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>254</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12 0</t>
+          <t>02 0</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>185</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>508</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>173</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>173</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71 2</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>179</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>193</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>60</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>139</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1168 2</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>954</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4247,17 +4247,17 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>856</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17 04</t>
+          <t>17 00</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>237</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1815 0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -4339,22 +4339,22 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>115</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>181</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>115 00</t>
+          <t>15 0</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>900</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2 7 9</t>
+          <t>2 1 2 8</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>270</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>581</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>078</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3809 1</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>248</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
@@ -5418,12 +5418,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>158</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>488</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>149</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>198</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>103</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -5944,17 +5944,17 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>554</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>654</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>118</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>505</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>218</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
